--- a/backend/data/financials_by_company/1B1.F.xlsx
+++ b/backend/data/financials_by_company/1B1.F.xlsx
@@ -647,7 +647,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -656,131 +656,131 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-27468045</v>
+        <v>-13335405</v>
       </c>
       <c r="E2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="F2" t="n">
-        <v>3819793</v>
+        <v>299817</v>
       </c>
       <c r="G2" t="n">
-        <v>3409009</v>
+        <v>2773490</v>
       </c>
       <c r="H2" t="n">
-        <v>-27468045</v>
+        <v>-13335405</v>
       </c>
       <c r="I2" t="n">
-        <v>-31287838</v>
+        <v>-13635222</v>
       </c>
       <c r="J2" t="n">
-        <v>1031159</v>
+        <v>-6474</v>
       </c>
       <c r="K2" t="n">
-        <v>90</v>
+        <v>1097</v>
       </c>
       <c r="L2" t="n">
-        <v>1125392</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="N2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="O2" t="n">
-        <v>32302165</v>
+        <v>13764699</v>
       </c>
       <c r="P2" t="n">
-        <v>-32302165</v>
+        <v>-13764299</v>
       </c>
       <c r="Q2" t="n">
-        <v>20203200</v>
+        <v>13955895</v>
       </c>
       <c r="R2" t="n">
-        <v>20203200</v>
+        <v>13951571</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.55</v>
+        <v>-0.98</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.55</v>
+        <v>-0.98</v>
       </c>
       <c r="U2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="V2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-31287928</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
+        <v>-13636319</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>-31287928</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
+        <v>-13636319</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
       <c r="AE2" t="n">
-        <v>1031159</v>
+        <v>-6474</v>
       </c>
       <c r="AF2" t="n">
-        <v>94143</v>
+        <v>5378</v>
       </c>
       <c r="AG2" t="n">
-        <v>90</v>
+        <v>1097</v>
       </c>
       <c r="AH2" t="n">
-        <v>1125392</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>-32302165</v>
+        <v>-13764299</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28893156</v>
+        <v>10991209</v>
       </c>
       <c r="AK2" t="n">
-        <v>7872844</v>
+        <v>7183063</v>
       </c>
       <c r="AL2" t="n">
-        <v>3819793</v>
+        <v>299817</v>
       </c>
       <c r="AM2" t="n">
-        <v>3819793</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+        <v>299817</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>4026200</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>4026200</v>
+      </c>
       <c r="AP2" t="n">
-        <v>-3409009</v>
+        <v>-2773090</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3409009</v>
+        <v>2773490</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -789,131 +789,135 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-24493033</v>
+        <v>-13950535</v>
       </c>
       <c r="E3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="F3" t="n">
-        <v>2826158</v>
+        <v>1313155</v>
       </c>
       <c r="G3" t="n">
-        <v>4101710</v>
+        <v>1634566</v>
       </c>
       <c r="H3" t="n">
-        <v>-24493033</v>
+        <v>-13950535</v>
       </c>
       <c r="I3" t="n">
-        <v>-28373116</v>
+        <v>-15263690</v>
       </c>
       <c r="J3" t="n">
-        <v>4297163</v>
+        <v>1792949</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>4389733</v>
+        <v>1911223</v>
       </c>
       <c r="M3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="N3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="O3" t="n">
-        <v>32128145</v>
+        <v>16987402</v>
       </c>
       <c r="P3" t="n">
-        <v>-32128045</v>
+        <v>-16987402</v>
       </c>
       <c r="Q3" t="n">
-        <v>16836000</v>
+        <v>14030000</v>
       </c>
       <c r="R3" t="n">
-        <v>16836000</v>
+        <v>14030000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.69</v>
+        <v>-1.09</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.69</v>
+        <v>-1.09</v>
       </c>
       <c r="U3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="V3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
       <c r="AE3" t="n">
-        <v>4297163</v>
+        <v>1792949</v>
       </c>
       <c r="AF3" t="n">
-        <v>92569</v>
+        <v>118267</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH3" t="n">
-        <v>4389733</v>
+        <v>1911223</v>
       </c>
       <c r="AI3" t="n">
-        <v>-32128045</v>
+        <v>-16987402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>28026435</v>
+        <v>15352836</v>
       </c>
       <c r="AK3" t="n">
-        <v>10832222</v>
+        <v>7789764</v>
       </c>
       <c r="AL3" t="n">
-        <v>3880083</v>
+        <v>1313155</v>
       </c>
       <c r="AM3" t="n">
-        <v>3880083</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+        <v>1313155</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6028241</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>6028241</v>
+      </c>
       <c r="AP3" t="n">
-        <v>-4101610</v>
+        <v>-1634566</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4101710</v>
+        <v>1634566</v>
       </c>
       <c r="AR3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -922,135 +926,131 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-13950535</v>
+        <v>-24493033</v>
       </c>
       <c r="E4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="F4" t="n">
-        <v>1313155</v>
+        <v>2826158</v>
       </c>
       <c r="G4" t="n">
-        <v>1634566</v>
+        <v>4101710</v>
       </c>
       <c r="H4" t="n">
-        <v>-13950535</v>
+        <v>-24493033</v>
       </c>
       <c r="I4" t="n">
-        <v>-15263690</v>
+        <v>-28373116</v>
       </c>
       <c r="J4" t="n">
-        <v>1792949</v>
+        <v>4297163</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>1911223</v>
+        <v>4389733</v>
       </c>
       <c r="M4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="N4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="O4" t="n">
-        <v>16987402</v>
+        <v>32128145</v>
       </c>
       <c r="P4" t="n">
-        <v>-16987402</v>
+        <v>-32128045</v>
       </c>
       <c r="Q4" t="n">
-        <v>14030000</v>
+        <v>16836000</v>
       </c>
       <c r="R4" t="n">
-        <v>14030000</v>
+        <v>16836000</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.09</v>
+        <v>-1.69</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.09</v>
+        <v>-1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="V4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
       <c r="AE4" t="n">
-        <v>1792949</v>
+        <v>4297163</v>
       </c>
       <c r="AF4" t="n">
-        <v>118267</v>
+        <v>92569</v>
       </c>
       <c r="AG4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1911223</v>
+        <v>4389733</v>
       </c>
       <c r="AI4" t="n">
-        <v>-16987402</v>
+        <v>-32128045</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15352836</v>
+        <v>28026435</v>
       </c>
       <c r="AK4" t="n">
-        <v>7789764</v>
+        <v>10832222</v>
       </c>
       <c r="AL4" t="n">
-        <v>1313155</v>
+        <v>3880083</v>
       </c>
       <c r="AM4" t="n">
-        <v>1313155</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6028241</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>6028241</v>
-      </c>
+        <v>3880083</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>-1634566</v>
+        <v>-4101610</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1634566</v>
+        <v>4101710</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1059,126 +1059,126 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-13335405</v>
+        <v>-27468045</v>
       </c>
       <c r="E5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="F5" t="n">
-        <v>299817</v>
+        <v>3819793</v>
       </c>
       <c r="G5" t="n">
-        <v>2773490</v>
+        <v>3409009</v>
       </c>
       <c r="H5" t="n">
-        <v>-13335405</v>
+        <v>-27468045</v>
       </c>
       <c r="I5" t="n">
-        <v>-13635222</v>
+        <v>-31287838</v>
       </c>
       <c r="J5" t="n">
-        <v>-6474</v>
+        <v>1031159</v>
       </c>
       <c r="K5" t="n">
-        <v>1097</v>
+        <v>90</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1125392</v>
       </c>
       <c r="M5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="N5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="O5" t="n">
-        <v>13764699</v>
+        <v>32302165</v>
       </c>
       <c r="P5" t="n">
-        <v>-13764299</v>
+        <v>-32302165</v>
       </c>
       <c r="Q5" t="n">
-        <v>13955895</v>
+        <v>20203200</v>
       </c>
       <c r="R5" t="n">
-        <v>13951571</v>
+        <v>20203200</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.98</v>
+        <v>-1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.98</v>
+        <v>-1.55</v>
       </c>
       <c r="U5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="V5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-13636319</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>-31287928</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
       <c r="Z5" t="n">
-        <v>-13636319</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+        <v>-31287928</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
       <c r="AB5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6474</v>
+        <v>1031159</v>
       </c>
       <c r="AF5" t="n">
-        <v>5378</v>
+        <v>94143</v>
       </c>
       <c r="AG5" t="n">
-        <v>1097</v>
+        <v>90</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>1125392</v>
       </c>
       <c r="AI5" t="n">
-        <v>-13764299</v>
+        <v>-32302165</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10991209</v>
+        <v>28893156</v>
       </c>
       <c r="AK5" t="n">
-        <v>7183063</v>
+        <v>7872844</v>
       </c>
       <c r="AL5" t="n">
-        <v>299817</v>
+        <v>3819793</v>
       </c>
       <c r="AM5" t="n">
-        <v>299817</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>4026200</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>4026200</v>
-      </c>
+        <v>3819793</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-2773090</v>
+        <v>-3409009</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2773490</v>
+        <v>3409009</v>
       </c>
       <c r="AR5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1479,676 +1479,676 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>20203200</v>
+        <v>13951571</v>
       </c>
       <c r="C2" t="n">
-        <v>20203200</v>
+        <v>13951571</v>
       </c>
       <c r="D2" t="n">
-        <v>7232820</v>
+        <v>6008858</v>
       </c>
       <c r="E2" t="n">
-        <v>49433849</v>
+        <v>115491993</v>
       </c>
       <c r="F2" t="n">
-        <v>103407628</v>
+        <v>141143534</v>
       </c>
       <c r="G2" t="n">
-        <v>45138940</v>
+        <v>109776901</v>
       </c>
       <c r="H2" t="n">
-        <v>49433849</v>
+        <v>115491993</v>
       </c>
       <c r="I2" t="n">
-        <v>7232820</v>
+        <v>6008858</v>
       </c>
       <c r="J2" t="n">
-        <v>103407628</v>
+        <v>141143534</v>
       </c>
       <c r="K2" t="n">
-        <v>103407628</v>
+        <v>141143534</v>
       </c>
       <c r="L2" t="n">
-        <v>103407628</v>
+        <v>141143534</v>
       </c>
       <c r="M2" t="n">
-        <v>103407628</v>
+        <v>141143534</v>
       </c>
       <c r="N2" t="n">
-        <v>-81280138</v>
+        <v>39882297</v>
       </c>
       <c r="O2" t="n">
-        <v>180393515</v>
+        <v>98153259</v>
       </c>
       <c r="P2" t="n">
-        <v>202032</v>
+        <v>139516</v>
       </c>
       <c r="Q2" t="n">
-        <v>202032</v>
+        <v>139516</v>
       </c>
       <c r="R2" t="n">
-        <v>10313871</v>
+        <v>10447179</v>
       </c>
       <c r="S2" t="n">
-        <v>5197099</v>
+        <v>4282230</v>
       </c>
       <c r="T2" t="n">
-        <v>42269</v>
+        <v>72432</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>104214</v>
+        <v>10933</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>5050616</v>
+        <v>4198865</v>
       </c>
       <c r="Y2" t="n">
-        <v>5050616</v>
+        <v>4198865</v>
       </c>
       <c r="Z2" t="n">
-        <v>5116772</v>
+        <v>6164949</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>2182204</v>
+        <v>1809993</v>
       </c>
       <c r="AC2" t="n">
-        <v>2182204</v>
+        <v>1809993</v>
       </c>
       <c r="AD2" t="n">
-        <v>874625</v>
+        <v>1244016</v>
       </c>
       <c r="AE2" t="n">
-        <v>101459</v>
+        <v>326277</v>
       </c>
       <c r="AF2" t="n">
-        <v>1931435</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>2424103</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>117020</v>
+      </c>
       <c r="AH2" t="n">
-        <v>102632</v>
+        <v>321605</v>
       </c>
       <c r="AI2" t="n">
-        <v>1828803</v>
+        <v>1985478</v>
       </c>
       <c r="AJ2" t="n">
-        <v>113721499</v>
+        <v>151590713</v>
       </c>
       <c r="AK2" t="n">
-        <v>63465787</v>
+        <v>35648863</v>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>53973779</v>
+        <v>25651541</v>
       </c>
       <c r="AO2" t="n">
-        <v>53973779</v>
+        <v>25651541</v>
       </c>
       <c r="AP2" t="n">
-        <v>9492008</v>
+        <v>9997322</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-13218433</v>
+        <v>-7867836</v>
       </c>
       <c r="AR2" t="n">
-        <v>22710441</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>17865158</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>180000</v>
+      </c>
       <c r="AT2" t="n">
-        <v>15379211</v>
+        <v>12305467</v>
       </c>
       <c r="AU2" t="n">
-        <v>890873</v>
+        <v>592929</v>
       </c>
       <c r="AV2" t="n">
-        <v>6440357</v>
+        <v>4786762</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>50255712</v>
+        <v>115941850</v>
       </c>
       <c r="AY2" t="n">
-        <v>615020</v>
+        <v>457098</v>
       </c>
       <c r="AZ2" t="n">
-        <v>30316206</v>
+        <v>916</v>
       </c>
       <c r="BA2" t="n">
-        <v>1136284</v>
+        <v>13444521</v>
       </c>
       <c r="BB2" t="n">
-        <v>18188202</v>
+        <v>102039315</v>
       </c>
       <c r="BC2" t="n">
-        <v>18188202</v>
+        <v>102039315</v>
       </c>
       <c r="BD2" t="n">
-        <v>15591142</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>2597060</v>
+        <v>102039315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>16836000</v>
+        <v>14030000</v>
       </c>
       <c r="C3" t="n">
-        <v>16836000</v>
+        <v>14030000</v>
       </c>
       <c r="D3" t="n">
-        <v>7139393</v>
+        <v>6408055</v>
       </c>
       <c r="E3" t="n">
-        <v>64970762</v>
+        <v>75002176</v>
       </c>
       <c r="F3" t="n">
-        <v>100930175</v>
+        <v>126447925</v>
       </c>
       <c r="G3" t="n">
-        <v>59669734</v>
+        <v>68009706</v>
       </c>
       <c r="H3" t="n">
-        <v>64970762</v>
+        <v>75002176</v>
       </c>
       <c r="I3" t="n">
-        <v>7139393</v>
+        <v>6408055</v>
       </c>
       <c r="J3" t="n">
-        <v>100930175</v>
+        <v>126447925</v>
       </c>
       <c r="K3" t="n">
-        <v>100930175</v>
+        <v>126447925</v>
       </c>
       <c r="L3" t="n">
-        <v>100930175</v>
+        <v>126447925</v>
       </c>
       <c r="M3" t="n">
-        <v>100930175</v>
+        <v>126447925</v>
       </c>
       <c r="N3" t="n">
-        <v>-49992210</v>
+        <v>24618600</v>
       </c>
       <c r="O3" t="n">
-        <v>150710949</v>
+        <v>101197609</v>
       </c>
       <c r="P3" t="n">
-        <v>168360</v>
+        <v>140300</v>
       </c>
       <c r="Q3" t="n">
-        <v>168360</v>
+        <v>140300</v>
       </c>
       <c r="R3" t="n">
-        <v>11344699</v>
+        <v>11613226</v>
       </c>
       <c r="S3" t="n">
-        <v>5302187</v>
+        <v>4633635</v>
       </c>
       <c r="T3" t="n">
-        <v>108311</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>83905</v>
+      </c>
+      <c r="U3" t="n">
+        <v>205084</v>
+      </c>
       <c r="V3" t="n">
-        <v>218055</v>
+        <v>141936</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4975821</v>
+        <v>4202710</v>
       </c>
       <c r="Y3" t="n">
-        <v>4975821</v>
+        <v>4202710</v>
       </c>
       <c r="Z3" t="n">
-        <v>6042512</v>
+        <v>6979591</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AB3" t="n">
-        <v>2163572</v>
+        <v>2205345</v>
       </c>
       <c r="AC3" t="n">
-        <v>2163572</v>
+        <v>2205345</v>
       </c>
       <c r="AD3" t="n">
-        <v>709802</v>
+        <v>1304879</v>
       </c>
       <c r="AE3" t="n">
-        <v>43550</v>
+        <v>113000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3017459</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>3282891</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>300</v>
+      </c>
       <c r="AH3" t="n">
-        <v>711</v>
+        <v>459784</v>
       </c>
       <c r="AI3" t="n">
-        <v>3016748</v>
+        <v>2822807</v>
       </c>
       <c r="AJ3" t="n">
-        <v>112274874</v>
+        <v>138061151</v>
       </c>
       <c r="AK3" t="n">
-        <v>46562628</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>63071854</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-1</v>
+      </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>35959413</v>
+        <v>51445749</v>
       </c>
       <c r="AO3" t="n">
-        <v>35959413</v>
+        <v>51445749</v>
       </c>
       <c r="AP3" t="n">
-        <v>10603215</v>
+        <v>11626106</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-11562083</v>
+        <v>-9675713</v>
       </c>
       <c r="AR3" t="n">
-        <v>22165298</v>
+        <v>21301819</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>14792308</v>
+        <v>15010396</v>
       </c>
       <c r="AU3" t="n">
-        <v>963616</v>
+        <v>921803</v>
       </c>
       <c r="AV3" t="n">
-        <v>6409374</v>
+        <v>5369620</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>65712246</v>
+        <v>74989297</v>
       </c>
       <c r="AY3" t="n">
-        <v>869512</v>
+        <v>939871</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9637</v>
+        <v>15386</v>
       </c>
       <c r="BA3" t="n">
-        <v>844957</v>
+        <v>8416255</v>
       </c>
       <c r="BB3" t="n">
-        <v>63988140</v>
+        <v>65617785</v>
       </c>
       <c r="BC3" t="n">
-        <v>63988140</v>
+        <v>65617785</v>
       </c>
       <c r="BD3" t="n">
-        <v>53510181</v>
+        <v>53015437</v>
       </c>
       <c r="BE3" t="n">
-        <v>10477959</v>
+        <v>12602348</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>14030000</v>
+        <v>16836000</v>
       </c>
       <c r="C4" t="n">
-        <v>14030000</v>
+        <v>16836000</v>
       </c>
       <c r="D4" t="n">
-        <v>6408055</v>
+        <v>7139393</v>
       </c>
       <c r="E4" t="n">
-        <v>75002176</v>
+        <v>64970762</v>
       </c>
       <c r="F4" t="n">
-        <v>126447925</v>
+        <v>100930175</v>
       </c>
       <c r="G4" t="n">
-        <v>68009706</v>
+        <v>59669734</v>
       </c>
       <c r="H4" t="n">
-        <v>75002176</v>
+        <v>64970762</v>
       </c>
       <c r="I4" t="n">
-        <v>6408055</v>
+        <v>7139393</v>
       </c>
       <c r="J4" t="n">
-        <v>126447925</v>
+        <v>100930175</v>
       </c>
       <c r="K4" t="n">
-        <v>126447925</v>
+        <v>100930175</v>
       </c>
       <c r="L4" t="n">
-        <v>126447925</v>
+        <v>100930175</v>
       </c>
       <c r="M4" t="n">
-        <v>126447925</v>
+        <v>100930175</v>
       </c>
       <c r="N4" t="n">
-        <v>24618600</v>
+        <v>-49992210</v>
       </c>
       <c r="O4" t="n">
-        <v>101197609</v>
+        <v>150710949</v>
       </c>
       <c r="P4" t="n">
-        <v>140300</v>
+        <v>168360</v>
       </c>
       <c r="Q4" t="n">
-        <v>140300</v>
+        <v>168360</v>
       </c>
       <c r="R4" t="n">
-        <v>11613226</v>
+        <v>11344699</v>
       </c>
       <c r="S4" t="n">
-        <v>4633635</v>
+        <v>5302187</v>
       </c>
       <c r="T4" t="n">
-        <v>83905</v>
-      </c>
-      <c r="U4" t="n">
-        <v>205084</v>
-      </c>
+        <v>108311</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>141936</v>
+        <v>218055</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4202710</v>
+        <v>4975821</v>
       </c>
       <c r="Y4" t="n">
-        <v>4202710</v>
+        <v>4975821</v>
       </c>
       <c r="Z4" t="n">
-        <v>6979591</v>
+        <v>6042512</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>2205345</v>
+        <v>2163572</v>
       </c>
       <c r="AC4" t="n">
-        <v>2205345</v>
+        <v>2163572</v>
       </c>
       <c r="AD4" t="n">
-        <v>1304879</v>
+        <v>709802</v>
       </c>
       <c r="AE4" t="n">
-        <v>113000</v>
+        <v>43550</v>
       </c>
       <c r="AF4" t="n">
-        <v>3282891</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>300</v>
-      </c>
+        <v>3017459</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>459784</v>
+        <v>711</v>
       </c>
       <c r="AI4" t="n">
-        <v>2822807</v>
+        <v>3016748</v>
       </c>
       <c r="AJ4" t="n">
-        <v>138061151</v>
+        <v>112274874</v>
       </c>
       <c r="AK4" t="n">
-        <v>63071854</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-1</v>
-      </c>
+        <v>46562628</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>51445749</v>
+        <v>35959413</v>
       </c>
       <c r="AO4" t="n">
-        <v>51445749</v>
+        <v>35959413</v>
       </c>
       <c r="AP4" t="n">
-        <v>11626106</v>
+        <v>10603215</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-9675713</v>
+        <v>-11562083</v>
       </c>
       <c r="AR4" t="n">
-        <v>21301819</v>
+        <v>22165298</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>15010396</v>
+        <v>14792308</v>
       </c>
       <c r="AU4" t="n">
-        <v>921803</v>
+        <v>963616</v>
       </c>
       <c r="AV4" t="n">
-        <v>5369620</v>
+        <v>6409374</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>74989297</v>
+        <v>65712246</v>
       </c>
       <c r="AY4" t="n">
-        <v>939871</v>
+        <v>869512</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15386</v>
+        <v>9637</v>
       </c>
       <c r="BA4" t="n">
-        <v>8416255</v>
+        <v>844957</v>
       </c>
       <c r="BB4" t="n">
-        <v>65617785</v>
+        <v>63988140</v>
       </c>
       <c r="BC4" t="n">
-        <v>65617785</v>
+        <v>63988140</v>
       </c>
       <c r="BD4" t="n">
-        <v>53015437</v>
+        <v>53510181</v>
       </c>
       <c r="BE4" t="n">
-        <v>12602348</v>
+        <v>10477959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>13951571</v>
+        <v>20203200</v>
       </c>
       <c r="C5" t="n">
-        <v>13951571</v>
+        <v>20203200</v>
       </c>
       <c r="D5" t="n">
-        <v>6008858</v>
+        <v>7232820</v>
       </c>
       <c r="E5" t="n">
-        <v>115491993</v>
+        <v>49433849</v>
       </c>
       <c r="F5" t="n">
-        <v>141143534</v>
+        <v>103407628</v>
       </c>
       <c r="G5" t="n">
-        <v>109776901</v>
+        <v>45138940</v>
       </c>
       <c r="H5" t="n">
-        <v>115491993</v>
+        <v>49433849</v>
       </c>
       <c r="I5" t="n">
-        <v>6008858</v>
+        <v>7232820</v>
       </c>
       <c r="J5" t="n">
-        <v>141143534</v>
+        <v>103407628</v>
       </c>
       <c r="K5" t="n">
-        <v>141143534</v>
+        <v>103407628</v>
       </c>
       <c r="L5" t="n">
-        <v>141143534</v>
+        <v>103407628</v>
       </c>
       <c r="M5" t="n">
-        <v>141143534</v>
+        <v>103407628</v>
       </c>
       <c r="N5" t="n">
-        <v>39882297</v>
+        <v>-81280138</v>
       </c>
       <c r="O5" t="n">
-        <v>98153259</v>
+        <v>180393515</v>
       </c>
       <c r="P5" t="n">
-        <v>139516</v>
+        <v>202032</v>
       </c>
       <c r="Q5" t="n">
-        <v>139516</v>
+        <v>202032</v>
       </c>
       <c r="R5" t="n">
-        <v>10447179</v>
+        <v>10313871</v>
       </c>
       <c r="S5" t="n">
-        <v>4282230</v>
+        <v>5197099</v>
       </c>
       <c r="T5" t="n">
-        <v>72432</v>
+        <v>42269</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>10933</v>
+        <v>104214</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4198865</v>
+        <v>5050616</v>
       </c>
       <c r="Y5" t="n">
-        <v>4198865</v>
+        <v>5050616</v>
       </c>
       <c r="Z5" t="n">
-        <v>6164949</v>
+        <v>5116772</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1809993</v>
+        <v>2182204</v>
       </c>
       <c r="AC5" t="n">
-        <v>1809993</v>
+        <v>2182204</v>
       </c>
       <c r="AD5" t="n">
-        <v>1244016</v>
+        <v>874625</v>
       </c>
       <c r="AE5" t="n">
-        <v>326277</v>
+        <v>101459</v>
       </c>
       <c r="AF5" t="n">
-        <v>2424103</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>117020</v>
-      </c>
+        <v>1931435</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>321605</v>
+        <v>102632</v>
       </c>
       <c r="AI5" t="n">
-        <v>1985478</v>
+        <v>1828803</v>
       </c>
       <c r="AJ5" t="n">
-        <v>151590713</v>
+        <v>113721499</v>
       </c>
       <c r="AK5" t="n">
-        <v>35648863</v>
+        <v>63465787</v>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>25651541</v>
+        <v>53973779</v>
       </c>
       <c r="AO5" t="n">
-        <v>25651541</v>
+        <v>53973779</v>
       </c>
       <c r="AP5" t="n">
-        <v>9997322</v>
+        <v>9492008</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-7867836</v>
+        <v>-13218433</v>
       </c>
       <c r="AR5" t="n">
-        <v>17865158</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>180000</v>
-      </c>
+        <v>22710441</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>12305467</v>
+        <v>15379211</v>
       </c>
       <c r="AU5" t="n">
-        <v>592929</v>
+        <v>890873</v>
       </c>
       <c r="AV5" t="n">
-        <v>4786762</v>
+        <v>6440357</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>115941850</v>
+        <v>50255712</v>
       </c>
       <c r="AY5" t="n">
-        <v>457098</v>
+        <v>615020</v>
       </c>
       <c r="AZ5" t="n">
-        <v>916</v>
+        <v>30316206</v>
       </c>
       <c r="BA5" t="n">
-        <v>13444521</v>
+        <v>1136284</v>
       </c>
       <c r="BB5" t="n">
-        <v>102039315</v>
+        <v>18188202</v>
       </c>
       <c r="BC5" t="n">
-        <v>102039315</v>
+        <v>18188202</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>15591142</v>
       </c>
       <c r="BE5" t="n">
-        <v>102039315</v>
+        <v>2597060</v>
       </c>
     </row>
   </sheetData>
@@ -2309,350 +2309,350 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-80764469</v>
+        <v>-32330978</v>
       </c>
       <c r="C2" t="n">
-        <v>29716238</v>
+        <v>4838680</v>
       </c>
       <c r="D2" t="n">
-        <v>-23774150</v>
+        <v>-18834561</v>
       </c>
       <c r="E2" t="n">
-        <v>18188202</v>
+        <v>102039315</v>
       </c>
       <c r="F2" t="n">
-        <v>63988140</v>
+        <v>120502324</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-45799938</v>
+        <v>-18463009</v>
       </c>
       <c r="I2" t="n">
-        <v>34760915</v>
+        <v>13856788</v>
       </c>
       <c r="J2" t="n">
-        <v>5139124</v>
+        <v>8289922</v>
       </c>
       <c r="K2" t="n">
-        <v>29716238</v>
+        <v>4838680</v>
       </c>
       <c r="L2" t="n">
-        <v>29716238</v>
+        <v>4838680</v>
       </c>
       <c r="M2" t="n">
-        <v>-23570534</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-18823380</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-16382014</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-16382014</v>
+      </c>
       <c r="P2" t="n">
-        <v>-451716</v>
+        <v>-2441366</v>
       </c>
       <c r="Q2" t="n">
-        <v>203616</v>
+        <v>11181</v>
       </c>
       <c r="R2" t="n">
-        <v>-655332</v>
+        <v>-2452547</v>
       </c>
       <c r="S2" t="n">
-        <v>-23118818</v>
+        <v>-16382014</v>
       </c>
       <c r="T2" t="n">
-        <v>-56990319</v>
+        <v>-13496417</v>
       </c>
       <c r="U2" t="n">
-        <v>-31374234</v>
+        <v>-1840912</v>
       </c>
       <c r="V2" t="n">
-        <v>-1054681</v>
+        <v>1346384</v>
       </c>
       <c r="W2" t="n">
-        <v>62913</v>
+        <v>-2769297</v>
       </c>
       <c r="X2" t="n">
-        <v>-30343405</v>
+        <v>-634857</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2197094</v>
+        <v>-1167510</v>
       </c>
       <c r="Z2" t="n">
-        <v>4039546</v>
+        <v>2835000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3819793</v>
+        <v>299817</v>
       </c>
       <c r="AB2" t="n">
-        <v>3819793</v>
+        <v>299817</v>
       </c>
       <c r="AC2" t="n">
-        <v>-31287928</v>
+        <v>-13636319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-57178164</v>
+        <v>-43844733</v>
       </c>
       <c r="C3" t="n">
-        <v>49099800</v>
+        <v>117020</v>
       </c>
       <c r="D3" t="n">
-        <v>-33888124</v>
+        <v>-33631350</v>
       </c>
       <c r="E3" t="n">
-        <v>63988140</v>
+        <v>65617785</v>
       </c>
       <c r="F3" t="n">
-        <v>65617785</v>
+        <v>102039315</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1629645</v>
+        <v>-36421530</v>
       </c>
       <c r="I3" t="n">
-        <v>55533484</v>
+        <v>7377360</v>
       </c>
       <c r="J3" t="n">
-        <v>5848971</v>
+        <v>6987866</v>
       </c>
       <c r="K3" t="n">
-        <v>49099800</v>
+        <v>117020</v>
       </c>
       <c r="L3" t="n">
-        <v>49099800</v>
+        <v>117020</v>
       </c>
       <c r="M3" t="n">
-        <v>-33873089</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-33585507</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-30312565</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-30312565</v>
+      </c>
       <c r="P3" t="n">
-        <v>-347198</v>
+        <v>-3272942</v>
       </c>
       <c r="Q3" t="n">
-        <v>15035</v>
+        <v>45843</v>
       </c>
       <c r="R3" t="n">
-        <v>-362233</v>
+        <v>-3318785</v>
       </c>
       <c r="S3" t="n">
-        <v>-33525891</v>
+        <v>-30312565</v>
       </c>
       <c r="T3" t="n">
-        <v>-23290040</v>
+        <v>-10213383</v>
       </c>
       <c r="U3" t="n">
-        <v>5916200</v>
+        <v>4898677</v>
       </c>
       <c r="V3" t="n">
-        <v>-1025176</v>
+        <v>1414173</v>
       </c>
       <c r="W3" t="n">
-        <v>-718681</v>
+        <v>-720252</v>
       </c>
       <c r="X3" t="n">
-        <v>7647405</v>
+        <v>4531023</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3652543</v>
+        <v>-1612585</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>441600</v>
       </c>
       <c r="AA3" t="n">
-        <v>2826158</v>
+        <v>1313155</v>
       </c>
       <c r="AB3" t="n">
-        <v>2826158</v>
+        <v>1313155</v>
       </c>
       <c r="AC3" t="n">
-        <v>-28373117</v>
+        <v>-15263697</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-43844733</v>
+        <v>-57178164</v>
       </c>
       <c r="C4" t="n">
-        <v>117020</v>
+        <v>49099800</v>
       </c>
       <c r="D4" t="n">
-        <v>-33631350</v>
+        <v>-33888124</v>
       </c>
       <c r="E4" t="n">
+        <v>63988140</v>
+      </c>
+      <c r="F4" t="n">
         <v>65617785</v>
       </c>
-      <c r="F4" t="n">
-        <v>102039315</v>
-      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-36421530</v>
+        <v>-1629645</v>
       </c>
       <c r="I4" t="n">
-        <v>7377360</v>
+        <v>55533484</v>
       </c>
       <c r="J4" t="n">
-        <v>6987866</v>
+        <v>5848971</v>
       </c>
       <c r="K4" t="n">
-        <v>117020</v>
+        <v>49099800</v>
       </c>
       <c r="L4" t="n">
-        <v>117020</v>
+        <v>49099800</v>
       </c>
       <c r="M4" t="n">
-        <v>-33585507</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-30312565</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-30312565</v>
-      </c>
+        <v>-33873089</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-3272942</v>
+        <v>-347198</v>
       </c>
       <c r="Q4" t="n">
-        <v>45843</v>
+        <v>15035</v>
       </c>
       <c r="R4" t="n">
-        <v>-3318785</v>
+        <v>-362233</v>
       </c>
       <c r="S4" t="n">
-        <v>-30312565</v>
+        <v>-33525891</v>
       </c>
       <c r="T4" t="n">
-        <v>-10213383</v>
+        <v>-23290040</v>
       </c>
       <c r="U4" t="n">
-        <v>4898677</v>
+        <v>5916200</v>
       </c>
       <c r="V4" t="n">
-        <v>1414173</v>
+        <v>-1025176</v>
       </c>
       <c r="W4" t="n">
-        <v>-720252</v>
+        <v>-718681</v>
       </c>
       <c r="X4" t="n">
-        <v>4531023</v>
+        <v>7647405</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1612585</v>
+        <v>-3652543</v>
       </c>
       <c r="Z4" t="n">
-        <v>441600</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1313155</v>
+        <v>2826158</v>
       </c>
       <c r="AB4" t="n">
-        <v>1313155</v>
+        <v>2826158</v>
       </c>
       <c r="AC4" t="n">
-        <v>-15263697</v>
+        <v>-28373117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-32330978</v>
+        <v>-80764469</v>
       </c>
       <c r="C5" t="n">
-        <v>4838680</v>
+        <v>29716238</v>
       </c>
       <c r="D5" t="n">
-        <v>-18834561</v>
+        <v>-23774150</v>
       </c>
       <c r="E5" t="n">
-        <v>102039315</v>
+        <v>18188202</v>
       </c>
       <c r="F5" t="n">
-        <v>120502324</v>
+        <v>63988140</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-18463009</v>
+        <v>-45799938</v>
       </c>
       <c r="I5" t="n">
-        <v>13856788</v>
+        <v>34760915</v>
       </c>
       <c r="J5" t="n">
-        <v>8289922</v>
+        <v>5139124</v>
       </c>
       <c r="K5" t="n">
-        <v>4838680</v>
+        <v>29716238</v>
       </c>
       <c r="L5" t="n">
-        <v>4838680</v>
+        <v>29716238</v>
       </c>
       <c r="M5" t="n">
-        <v>-18823380</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-16382014</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-16382014</v>
-      </c>
+        <v>-23570534</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-2441366</v>
+        <v>-451716</v>
       </c>
       <c r="Q5" t="n">
-        <v>11181</v>
+        <v>203616</v>
       </c>
       <c r="R5" t="n">
-        <v>-2452547</v>
+        <v>-655332</v>
       </c>
       <c r="S5" t="n">
-        <v>-16382014</v>
+        <v>-23118818</v>
       </c>
       <c r="T5" t="n">
-        <v>-13496417</v>
+        <v>-56990319</v>
       </c>
       <c r="U5" t="n">
-        <v>-1840912</v>
+        <v>-31374234</v>
       </c>
       <c r="V5" t="n">
-        <v>1346384</v>
+        <v>-1054681</v>
       </c>
       <c r="W5" t="n">
-        <v>-2769297</v>
+        <v>62913</v>
       </c>
       <c r="X5" t="n">
-        <v>-634857</v>
+        <v>-30343405</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1167510</v>
+        <v>-2197094</v>
       </c>
       <c r="Z5" t="n">
-        <v>2835000</v>
+        <v>4039546</v>
       </c>
       <c r="AA5" t="n">
-        <v>299817</v>
+        <v>3819793</v>
       </c>
       <c r="AB5" t="n">
-        <v>299817</v>
+        <v>3819793</v>
       </c>
       <c r="AC5" t="n">
-        <v>-13636319</v>
+        <v>-31287928</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL2"/>
+  <dimension ref="A1:DK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,510 +2742,505 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>compensationAsOfEpochDate</t>
+          <t>executiveTeam</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>executiveTeam</t>
+          <t>maxAge</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>maxAge</t>
+          <t>priceHint</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>priceHint</t>
+          <t>previousClose</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>previousClose</t>
+          <t>open</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>dayLow</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>dayLow</t>
+          <t>dayHigh</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>dayHigh</t>
+          <t>regularMarketPreviousClose</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>regularMarketPreviousClose</t>
+          <t>regularMarketOpen</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>regularMarketOpen</t>
+          <t>regularMarketDayLow</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>regularMarketDayLow</t>
+          <t>regularMarketDayHigh</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>regularMarketDayHigh</t>
+          <t>payoutRatio</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>corporateActions</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>corporateActions</t>
+          <t>regularMarketTime</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>regularMarketTime</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>exchange</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>messageBoardId</t>
+          <t>exchangeTimezoneName</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>exchangeTimezoneName</t>
+          <t>exchangeTimezoneShortName</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>exchangeTimezoneShortName</t>
+          <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>gmtOffSetMilliseconds</t>
+          <t>market</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>market</t>
+          <t>esgPopulated</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>esgPopulated</t>
+          <t>hasPrePostMarketData</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>cryptoTradeable</t>
+          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>regularMarketChangePercent</t>
+          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3319,363 +3314,360 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Marcin Jan Szumowski Ph.D.', 'title': 'Co-Founder, CEO &amp; President of Management Board', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Zbigniew  Zaslona', 'title': 'Chief Scientific Officer &amp; Member of Management Board', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Piotr  Iwanowski', 'title': 'Chief Medical Officer &amp; Member of Management Board', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Agnieszka  Rajczuk-Szczepanska', 'title': 'HR Director', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Adam  Golebiowski Ph.D.', 'title': 'Co-Founder &amp; VP of Research Chemistry', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jacek  Olczak Ph.D.', 'title': 'Co-Founder &amp; Head of Medicinal Chemistry', 'fiscalYear': 2017, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Monika  Czarnecka', 'title': 'Finance Director', 'fiscalYear': 2017, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Magdalena  Tyszkiewicz', 'title': 'Head of CMC', 'fiscalYear': 2017, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>1514678400</v>
-      </c>
-      <c r="P2" t="inlineStr">
+          <t>[{'maxAge': 1, 'name': 'Dr. Marcin Jan Szumowski Ph.D.', 'title': 'Co-Founder, CEO &amp; President of Management Board', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Zbigniew  Zaslona', 'title': 'Chief Scientific Officer &amp; Member of Management Board', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>86400</v>
+      </c>
       <c r="Q2" t="n">
-        <v>86400</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>1.268</v>
       </c>
       <c r="S2" t="n">
-        <v>1.264</v>
+        <v>1.268</v>
       </c>
       <c r="T2" t="n">
-        <v>1.336</v>
+        <v>1.268</v>
       </c>
       <c r="U2" t="n">
-        <v>1.336</v>
+        <v>1.268</v>
       </c>
       <c r="V2" t="n">
-        <v>1.336</v>
+        <v>1.268</v>
       </c>
       <c r="W2" t="n">
-        <v>1.264</v>
+        <v>1.268</v>
       </c>
       <c r="X2" t="n">
-        <v>1.336</v>
+        <v>1.268</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.336</v>
+        <v>1.268</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.336</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.027</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.061</v>
+        <v>236</v>
       </c>
       <c r="AC2" t="n">
         <v>236</v>
       </c>
       <c r="AD2" t="n">
-        <v>236</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.396</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>31349760</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>32890324</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1.25944</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.50484</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-2.40642</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14408198</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>24723786</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.08375</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>24723786</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.29216588</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-0.053731322</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.268</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>-15631912</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>6.244</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-0.16272</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-2.53985</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-2.3977299</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>1B1.F</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="BY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CC2" t="n">
+        <v>1782108389</v>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>finmb_263531047</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CH2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="CJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1614841200000</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>1.268 - 1.268</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CP2" t="n">
         <v>6</v>
       </c>
-      <c r="AF2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.478</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>27525816</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28934391</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.23376</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1.52953</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="AU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-2.40642</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>14408198</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20603155</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.25215</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.08375</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>20603155</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.3078341</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BG2" t="n">
+      <c r="CQ2" t="n">
+        <v>0.11800003</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.102608725</v>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>1.15 - 2.02</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>-0.752</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>-0.37227723</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>-5.373132</v>
+      </c>
+      <c r="CW2" t="n">
         <v>-0.23</v>
       </c>
-      <c r="BH2" t="n">
-        <v>-0.027692318</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.336</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>-15631912</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>6.244</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-0.16272</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-2.53985</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>-2.3977299</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>1B1.F</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="BZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CD2" t="n">
-        <v>1780380716</v>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>finmb_263531047</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="CI2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="CK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CX2" t="n">
+        <v>0.008560061000000001</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.0067967204</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.23684001</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-0.15738551</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>OncoArendi Therapeutics S.A.</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
         <is>
           <t>Molecure S.A.</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
         <is>
           <t>OncoArendi Therapeutics S.A.  N</t>
         </is>
       </c>
-      <c r="CN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1614841200000</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.07199991</v>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>1.336 - 1.336</t>
-        </is>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="CS2" t="n">
-        <v>6</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0.18599999</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.16173913</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>1.15 - 2.02</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>-0.6840000000000001</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>-0.33861387</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>-2.7692318</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0.10223997</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.0828686</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.19353008</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-0.12652911</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>OncoArendi Therapeutics S.A.</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DI2" t="b">
+      <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>5.696195</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1.336</v>
-      </c>
-      <c r="DL2" t="inlineStr"/>
+        <v>1.268</v>
+      </c>
+      <c r="DK2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
